--- a/artfynd/A 22467-2025 artfynd.xlsx
+++ b/artfynd/A 22467-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127110788</v>
       </c>
       <c r="B3" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>127110512</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>127110270</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>127110668</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>127110838</v>
       </c>
       <c r="B7" t="n">
-        <v>80118</v>
+        <v>80149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 22467-2025 artfynd.xlsx
+++ b/artfynd/A 22467-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127110788</v>
       </c>
       <c r="B3" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>127110512</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>127110270</v>
       </c>
       <c r="B5" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>127110668</v>
       </c>
       <c r="B6" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>127110838</v>
       </c>
       <c r="B7" t="n">
-        <v>80149</v>
+        <v>80152</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 22467-2025 artfynd.xlsx
+++ b/artfynd/A 22467-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127110403</v>
       </c>
       <c r="B2" t="n">
-        <v>56840</v>
+        <v>56844</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>127110788</v>
       </c>
       <c r="B3" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>127110512</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>127110270</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>127110668</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>127110838</v>
       </c>
       <c r="B7" t="n">
-        <v>80152</v>
+        <v>80156</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 22467-2025 artfynd.xlsx
+++ b/artfynd/A 22467-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127110403</v>
       </c>
       <c r="B2" t="n">
-        <v>56844</v>
+        <v>56846</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>127110788</v>
       </c>
       <c r="B3" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>127110512</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>127110270</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>127110668</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>127110838</v>
       </c>
       <c r="B7" t="n">
-        <v>80156</v>
+        <v>80158</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 22467-2025 artfynd.xlsx
+++ b/artfynd/A 22467-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127110403</v>
       </c>
       <c r="B2" t="n">
-        <v>56846</v>
+        <v>56849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>127110788</v>
       </c>
       <c r="B3" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>127110512</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>127110270</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>127110668</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>127110838</v>
       </c>
       <c r="B7" t="n">
-        <v>80158</v>
+        <v>80161</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 22467-2025 artfynd.xlsx
+++ b/artfynd/A 22467-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127110403</v>
       </c>
       <c r="B2" t="n">
-        <v>56849</v>
+        <v>56855</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>127110788</v>
       </c>
       <c r="B3" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>127110512</v>
       </c>
       <c r="B4" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>127110270</v>
       </c>
       <c r="B5" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>127110668</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>127110838</v>
       </c>
       <c r="B7" t="n">
-        <v>80161</v>
+        <v>80167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
